--- a/src/src/main/webapp/portal/zkb/probe/ZKB_PROBE_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/probe/ZKB_PROBE_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503277717\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2EF882-704B-44B3-93A5-0C7F30914C8B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6940D14-39B6-45B1-8896-93766B892EB9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -41,15 +41,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>价值类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>是否有效</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>探头号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>价值类型</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -88,7 +88,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -111,11 +111,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -126,6 +137,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,7 +468,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -462,18 +476,21 @@
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
+      <c r="D1" s="6" t="s">
+        <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:E1048576" xr:uid="{8A3EC725-C6D7-44AB-939D-282FED68DD34}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{8A3EC725-C6D7-44AB-939D-282FED68DD34}">
       <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{AA913B57-C8B7-4437-B662-898FD33C5991}">
+      <formula1>"高值,普通,特殊"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/probe/ZKB_PROBE_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/probe/ZKB_PROBE_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503277717\Desktop\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\hc-apm-web\src\src\main\webapp\portal\zkb\probe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6940D14-39B6-45B1-8896-93766B892EB9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF30DCD-759B-401B-BACA-F4658439F69A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -88,7 +88,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -111,22 +111,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -137,9 +126,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,7 +462,7 @@
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
